--- a/artfynd/A 17107-2025 artfynd.xlsx
+++ b/artfynd/A 17107-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1030,6 +1030,112 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125961766</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91245</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Totthummelns östsida , Totthummelns östsida , Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>404816</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7031799</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Bördig grannaturskog i östsluttning</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17107-2025 artfynd.xlsx
+++ b/artfynd/A 17107-2025 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>125961766</v>
       </c>
       <c r="B5" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17107-2025 artfynd.xlsx
+++ b/artfynd/A 17107-2025 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>125961766</v>
       </c>
       <c r="B5" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17107-2025 artfynd.xlsx
+++ b/artfynd/A 17107-2025 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>125961766</v>
       </c>
       <c r="B5" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17107-2025 artfynd.xlsx
+++ b/artfynd/A 17107-2025 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>125961766</v>
       </c>
       <c r="B5" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17107-2025 artfynd.xlsx
+++ b/artfynd/A 17107-2025 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>125961766</v>
       </c>
       <c r="B5" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17107-2025 artfynd.xlsx
+++ b/artfynd/A 17107-2025 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>125961766</v>
       </c>
       <c r="B5" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17107-2025 artfynd.xlsx
+++ b/artfynd/A 17107-2025 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>125961766</v>
       </c>
       <c r="B5" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17107-2025 artfynd.xlsx
+++ b/artfynd/A 17107-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1136,6 +1136,524 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128479022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>95915</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2682</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kärrkammossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Helodium blandowii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(F.Weber &amp; D.Mohr) Warnst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tottbacken, Tottbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>405009</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7032063</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Grovvuxna skogsöar på skidbacke</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128479181</v>
+      </c>
+      <c r="B7" t="n">
+        <v>88761</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>510</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tottbacken, Tottbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>405203</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7032031</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Grovvuxna skogsöar på skidbacke</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128479163</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92057</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Tottbacken, Tottbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>405188</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7032094</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Grovvuxna skogsöar på skidbacke</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128478996</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92295</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Tottbacken, Tottbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>404965</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7032021</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Grovvuxna skogsöar på skidbacke</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128478995</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Tottbacken, Tottbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>404965</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7032021</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Grovvuxna skogsöar på skidbacke</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17107-2025 artfynd.xlsx
+++ b/artfynd/A 17107-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1141,7 +1141,7 @@
         <v>128479022</v>
       </c>
       <c r="B6" t="n">
-        <v>95915</v>
+        <v>96008</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>128479181</v>
       </c>
       <c r="B7" t="n">
-        <v>88761</v>
+        <v>88853</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>128479163</v>
       </c>
       <c r="B8" t="n">
-        <v>92057</v>
+        <v>92149</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1452,45 +1452,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128478996</v>
+        <v>128479322</v>
       </c>
       <c r="B9" t="n">
-        <v>92295</v>
+        <v>91470</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tottbacken, Tottbacken, Jmt</t>
+          <t>Totthummelns västsida, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>404965</v>
+        <v>405142</v>
       </c>
       <c r="R9" t="n">
-        <v>7032021</v>
+        <v>7031890</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,12 +1534,13 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Grovvuxna skogsöar på skidbacke</t>
+          <t>Översilad, sluten grannaturskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1554,32 +1558,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128478995</v>
+        <v>128478996</v>
       </c>
       <c r="B10" t="n">
-        <v>79032</v>
+        <v>92387</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1653,6 +1657,426 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128479384</v>
+      </c>
+      <c r="B11" t="n">
+        <v>88853</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>510</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Totthummelns västsida, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>405132</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7031872</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Översilad, sluten grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128478995</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tottbacken, Tottbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>404965</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7032021</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Grovvuxna skogsöar på skidbacke</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128479457</v>
+      </c>
+      <c r="B13" t="n">
+        <v>88709</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4405</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Diskvaxskivling</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hygrophorus discoideus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Pers.) Fr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Totthummelns västsida, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>405040</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7031813</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Översilad, sluten grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128479804</v>
+      </c>
+      <c r="B14" t="n">
+        <v>90223</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>245031</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Borgsjömusseron</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tricholoma borgsjoeënse</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Jacobsson &amp; Muskos</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Totthummelns västsida, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>404933</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7031810</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Översilad, sluten grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17107-2025 artfynd.xlsx
+++ b/artfynd/A 17107-2025 artfynd.xlsx
@@ -1766,45 +1766,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128478995</v>
+        <v>128479457</v>
       </c>
       <c r="B12" t="n">
-        <v>79083</v>
+        <v>88709</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>4405</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tottbacken, Tottbacken, Jmt</t>
+          <t>Totthummelns västsida, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>404965</v>
+        <v>405040</v>
       </c>
       <c r="R12" t="n">
-        <v>7032021</v>
+        <v>7031813</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1845,12 +1848,13 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Grovvuxna skogsöar på skidbacke</t>
+          <t>Översilad, sluten grannaturskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1868,48 +1872,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128479457</v>
+        <v>128478995</v>
       </c>
       <c r="B13" t="n">
-        <v>88709</v>
+        <v>79083</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4405</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Totthummelns västsida, Jmt</t>
+          <t>Tottbacken, Tottbacken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>405040</v>
+        <v>404965</v>
       </c>
       <c r="R13" t="n">
-        <v>7031813</v>
+        <v>7032021</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1950,13 +1951,12 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Översilad, sluten grannaturskog</t>
+          <t>Grovvuxna skogsöar på skidbacke</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 17107-2025 artfynd.xlsx
+++ b/artfynd/A 17107-2025 artfynd.xlsx
@@ -1766,32 +1766,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128479457</v>
+        <v>128479804</v>
       </c>
       <c r="B12" t="n">
-        <v>88709</v>
+        <v>90223</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4405</v>
+        <v>245031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Borgsjömusseron</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Tricholoma borgsjoeënse</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>Jacobsson &amp; Muskos</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>405040</v>
+        <v>404933</v>
       </c>
       <c r="R12" t="n">
-        <v>7031813</v>
+        <v>7031810</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1872,45 +1872,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128478995</v>
+        <v>128479457</v>
       </c>
       <c r="B13" t="n">
-        <v>79083</v>
+        <v>88709</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>4405</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tottbacken, Tottbacken, Jmt</t>
+          <t>Totthummelns västsida, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>404965</v>
+        <v>405040</v>
       </c>
       <c r="R13" t="n">
-        <v>7032021</v>
+        <v>7031813</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1951,12 +1954,13 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Grovvuxna skogsöar på skidbacke</t>
+          <t>Översilad, sluten grannaturskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1974,48 +1978,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128479804</v>
+        <v>128478995</v>
       </c>
       <c r="B14" t="n">
-        <v>90223</v>
+        <v>79083</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>245031</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Borgsjömusseron</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tricholoma borgsjoeënse</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Jacobsson &amp; Muskos</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Totthummelns västsida, Jmt</t>
+          <t>Tottbacken, Tottbacken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>404933</v>
+        <v>404965</v>
       </c>
       <c r="R14" t="n">
-        <v>7031810</v>
+        <v>7032021</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2056,13 +2057,12 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Översilad, sluten grannaturskog</t>
+          <t>Grovvuxna skogsöar på skidbacke</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 17107-2025 artfynd.xlsx
+++ b/artfynd/A 17107-2025 artfynd.xlsx
@@ -1141,7 +1141,7 @@
         <v>128479022</v>
       </c>
       <c r="B6" t="n">
-        <v>96008</v>
+        <v>96014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>128479181</v>
       </c>
       <c r="B7" t="n">
-        <v>88853</v>
+        <v>88859</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>128479163</v>
       </c>
       <c r="B8" t="n">
-        <v>92149</v>
+        <v>92155</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>128479322</v>
       </c>
       <c r="B9" t="n">
-        <v>91470</v>
+        <v>91476</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>128478996</v>
       </c>
       <c r="B10" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>128479384</v>
       </c>
       <c r="B11" t="n">
-        <v>88853</v>
+        <v>88859</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1766,32 +1766,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128479804</v>
+        <v>128479457</v>
       </c>
       <c r="B12" t="n">
-        <v>90223</v>
+        <v>88715</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>245031</v>
+        <v>4405</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Borgsjömusseron</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tricholoma borgsjoeënse</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Jacobsson &amp; Muskos</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>404933</v>
+        <v>405040</v>
       </c>
       <c r="R12" t="n">
-        <v>7031810</v>
+        <v>7031813</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1872,48 +1872,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128479457</v>
+        <v>128478995</v>
       </c>
       <c r="B13" t="n">
-        <v>88709</v>
+        <v>79087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4405</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Totthummelns västsida, Jmt</t>
+          <t>Tottbacken, Tottbacken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>405040</v>
+        <v>404965</v>
       </c>
       <c r="R13" t="n">
-        <v>7031813</v>
+        <v>7032021</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1954,13 +1951,12 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Översilad, sluten grannaturskog</t>
+          <t>Grovvuxna skogsöar på skidbacke</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1978,45 +1974,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128478995</v>
+        <v>128479804</v>
       </c>
       <c r="B14" t="n">
-        <v>79083</v>
+        <v>90229</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>245031</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Borgsjömusseron</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma borgsjoeënse</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Jacobsson &amp; Muskos</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tottbacken, Tottbacken, Jmt</t>
+          <t>Totthummelns västsida, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>404965</v>
+        <v>404933</v>
       </c>
       <c r="R14" t="n">
-        <v>7032021</v>
+        <v>7031810</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2057,12 +2056,13 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Grovvuxna skogsöar på skidbacke</t>
+          <t>Översilad, sluten grannaturskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 17107-2025 artfynd.xlsx
+++ b/artfynd/A 17107-2025 artfynd.xlsx
@@ -1141,7 +1141,7 @@
         <v>128479022</v>
       </c>
       <c r="B6" t="n">
-        <v>96014</v>
+        <v>96020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>128479181</v>
       </c>
       <c r="B7" t="n">
-        <v>88859</v>
+        <v>88865</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>128479163</v>
       </c>
       <c r="B8" t="n">
-        <v>92155</v>
+        <v>92161</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>128479322</v>
       </c>
       <c r="B9" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>128478996</v>
       </c>
       <c r="B10" t="n">
-        <v>92393</v>
+        <v>92399</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>128479384</v>
       </c>
       <c r="B11" t="n">
-        <v>88859</v>
+        <v>88865</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1766,48 +1766,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128479457</v>
+        <v>128478995</v>
       </c>
       <c r="B12" t="n">
-        <v>88715</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4405</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Totthummelns västsida, Jmt</t>
+          <t>Tottbacken, Tottbacken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>405040</v>
+        <v>404965</v>
       </c>
       <c r="R12" t="n">
-        <v>7031813</v>
+        <v>7032021</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1848,13 +1845,12 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Översilad, sluten grannaturskog</t>
+          <t>Grovvuxna skogsöar på skidbacke</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1872,45 +1868,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128478995</v>
+        <v>128479457</v>
       </c>
       <c r="B13" t="n">
-        <v>79087</v>
+        <v>88721</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>4405</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tottbacken, Tottbacken, Jmt</t>
+          <t>Totthummelns västsida, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>404965</v>
+        <v>405040</v>
       </c>
       <c r="R13" t="n">
-        <v>7032021</v>
+        <v>7031813</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1951,12 +1950,13 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Grovvuxna skogsöar på skidbacke</t>
+          <t>Översilad, sluten grannaturskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1977,7 +1977,7 @@
         <v>128479804</v>
       </c>
       <c r="B14" t="n">
-        <v>90229</v>
+        <v>90235</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 17107-2025 artfynd.xlsx
+++ b/artfynd/A 17107-2025 artfynd.xlsx
@@ -1141,7 +1141,7 @@
         <v>128479022</v>
       </c>
       <c r="B6" t="n">
-        <v>96020</v>
+        <v>96022</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>128479181</v>
       </c>
       <c r="B7" t="n">
-        <v>88865</v>
+        <v>88867</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,32 +1346,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128479163</v>
+        <v>128479322</v>
       </c>
       <c r="B8" t="n">
-        <v>92161</v>
+        <v>91484</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1380,14 +1380,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tottbacken, Tottbacken, Jmt</t>
+          <t>Totthummelns västsida, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>405188</v>
+        <v>405142</v>
       </c>
       <c r="R8" t="n">
-        <v>7032094</v>
+        <v>7031890</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Grovvuxna skogsöar på skidbacke</t>
+          <t>Översilad, sluten grannaturskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1452,32 +1452,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128479322</v>
+        <v>128479163</v>
       </c>
       <c r="B9" t="n">
-        <v>91482</v>
+        <v>92163</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1486,14 +1486,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Totthummelns västsida, Jmt</t>
+          <t>Tottbacken, Tottbacken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>405142</v>
+        <v>405188</v>
       </c>
       <c r="R9" t="n">
-        <v>7031890</v>
+        <v>7032094</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Översilad, sluten grannaturskog</t>
+          <t>Grovvuxna skogsöar på skidbacke</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1561,7 +1561,7 @@
         <v>128478996</v>
       </c>
       <c r="B10" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>128479384</v>
       </c>
       <c r="B11" t="n">
-        <v>88865</v>
+        <v>88867</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1766,45 +1766,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128478995</v>
+        <v>128479804</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>90237</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>245031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Borgsjömusseron</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma borgsjoeënse</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Jacobsson &amp; Muskos</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tottbacken, Tottbacken, Jmt</t>
+          <t>Totthummelns västsida, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>404965</v>
+        <v>404933</v>
       </c>
       <c r="R12" t="n">
-        <v>7032021</v>
+        <v>7031810</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1845,12 +1848,13 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Grovvuxna skogsöar på skidbacke</t>
+          <t>Översilad, sluten grannaturskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1871,7 +1875,7 @@
         <v>128479457</v>
       </c>
       <c r="B13" t="n">
-        <v>88721</v>
+        <v>88723</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1974,48 +1978,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128479804</v>
+        <v>128478995</v>
       </c>
       <c r="B14" t="n">
-        <v>90235</v>
+        <v>79089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>245031</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Borgsjömusseron</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tricholoma borgsjoeënse</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Jacobsson &amp; Muskos</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Totthummelns västsida, Jmt</t>
+          <t>Tottbacken, Tottbacken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>404933</v>
+        <v>404965</v>
       </c>
       <c r="R14" t="n">
-        <v>7031810</v>
+        <v>7032021</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2056,13 +2057,12 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Översilad, sluten grannaturskog</t>
+          <t>Grovvuxna skogsöar på skidbacke</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 17107-2025 artfynd.xlsx
+++ b/artfynd/A 17107-2025 artfynd.xlsx
@@ -1346,32 +1346,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128479322</v>
+        <v>128479163</v>
       </c>
       <c r="B8" t="n">
-        <v>91484</v>
+        <v>92163</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1380,14 +1380,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Totthummelns västsida, Jmt</t>
+          <t>Tottbacken, Tottbacken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>405142</v>
+        <v>405188</v>
       </c>
       <c r="R8" t="n">
-        <v>7031890</v>
+        <v>7032094</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Översilad, sluten grannaturskog</t>
+          <t>Grovvuxna skogsöar på skidbacke</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1452,32 +1452,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128479163</v>
+        <v>128479322</v>
       </c>
       <c r="B9" t="n">
-        <v>92163</v>
+        <v>91484</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1486,14 +1486,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tottbacken, Tottbacken, Jmt</t>
+          <t>Totthummelns västsida, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>405188</v>
+        <v>405142</v>
       </c>
       <c r="R9" t="n">
-        <v>7032094</v>
+        <v>7031890</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Grovvuxna skogsöar på skidbacke</t>
+          <t>Översilad, sluten grannaturskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1872,48 +1872,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128479457</v>
+        <v>128478995</v>
       </c>
       <c r="B13" t="n">
-        <v>88723</v>
+        <v>79089</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4405</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Totthummelns västsida, Jmt</t>
+          <t>Tottbacken, Tottbacken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>405040</v>
+        <v>404965</v>
       </c>
       <c r="R13" t="n">
-        <v>7031813</v>
+        <v>7032021</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1954,13 +1951,12 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Översilad, sluten grannaturskog</t>
+          <t>Grovvuxna skogsöar på skidbacke</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1978,45 +1974,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128478995</v>
+        <v>128479457</v>
       </c>
       <c r="B14" t="n">
-        <v>79089</v>
+        <v>88723</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4405</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tottbacken, Tottbacken, Jmt</t>
+          <t>Totthummelns västsida, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>404965</v>
+        <v>405040</v>
       </c>
       <c r="R14" t="n">
-        <v>7032021</v>
+        <v>7031813</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2057,12 +2056,13 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Grovvuxna skogsöar på skidbacke</t>
+          <t>Översilad, sluten grannaturskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 17107-2025 artfynd.xlsx
+++ b/artfynd/A 17107-2025 artfynd.xlsx
@@ -1766,48 +1766,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128479804</v>
+        <v>128478995</v>
       </c>
       <c r="B12" t="n">
-        <v>90237</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>245031</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Borgsjömusseron</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tricholoma borgsjoeënse</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Jacobsson &amp; Muskos</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Totthummelns västsida, Jmt</t>
+          <t>Tottbacken, Tottbacken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>404933</v>
+        <v>404965</v>
       </c>
       <c r="R12" t="n">
-        <v>7031810</v>
+        <v>7032021</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1848,13 +1845,12 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Översilad, sluten grannaturskog</t>
+          <t>Grovvuxna skogsöar på skidbacke</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1872,45 +1868,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128478995</v>
+        <v>128479804</v>
       </c>
       <c r="B13" t="n">
-        <v>79089</v>
+        <v>90237</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>245031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Borgsjömusseron</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma borgsjoeënse</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Jacobsson &amp; Muskos</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tottbacken, Tottbacken, Jmt</t>
+          <t>Totthummelns västsida, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>404965</v>
+        <v>404933</v>
       </c>
       <c r="R13" t="n">
-        <v>7032021</v>
+        <v>7031810</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1951,12 +1950,13 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Grovvuxna skogsöar på skidbacke</t>
+          <t>Översilad, sluten grannaturskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 17107-2025 artfynd.xlsx
+++ b/artfynd/A 17107-2025 artfynd.xlsx
@@ -1141,7 +1141,7 @@
         <v>128479022</v>
       </c>
       <c r="B6" t="n">
-        <v>96022</v>
+        <v>96023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>128479163</v>
       </c>
       <c r="B8" t="n">
-        <v>92163</v>
+        <v>92164</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>128479322</v>
       </c>
       <c r="B9" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>128478996</v>
       </c>
       <c r="B10" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1868,32 +1868,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128479804</v>
+        <v>128479457</v>
       </c>
       <c r="B13" t="n">
-        <v>90237</v>
+        <v>88723</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>245031</v>
+        <v>4405</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Borgsjömusseron</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tricholoma borgsjoeënse</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Jacobsson &amp; Muskos</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>404933</v>
+        <v>405040</v>
       </c>
       <c r="R13" t="n">
-        <v>7031810</v>
+        <v>7031813</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1974,32 +1974,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128479457</v>
+        <v>128479804</v>
       </c>
       <c r="B14" t="n">
-        <v>88723</v>
+        <v>90237</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4405</v>
+        <v>245031</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Borgsjömusseron</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Tricholoma borgsjoeënse</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>Jacobsson &amp; Muskos</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2012,10 +2012,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>405040</v>
+        <v>404933</v>
       </c>
       <c r="R14" t="n">
-        <v>7031813</v>
+        <v>7031810</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 17107-2025 artfynd.xlsx
+++ b/artfynd/A 17107-2025 artfynd.xlsx
@@ -1141,7 +1141,7 @@
         <v>128479022</v>
       </c>
       <c r="B6" t="n">
-        <v>96023</v>
+        <v>96050</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>128479181</v>
       </c>
       <c r="B7" t="n">
-        <v>88867</v>
+        <v>88894</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>128479163</v>
       </c>
       <c r="B8" t="n">
-        <v>92164</v>
+        <v>92191</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>128479322</v>
       </c>
       <c r="B9" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>128478996</v>
       </c>
       <c r="B10" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>128479384</v>
       </c>
       <c r="B11" t="n">
-        <v>88867</v>
+        <v>88894</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1766,45 +1766,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128478995</v>
+        <v>128479457</v>
       </c>
       <c r="B12" t="n">
-        <v>79089</v>
+        <v>88750</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>4405</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tottbacken, Tottbacken, Jmt</t>
+          <t>Totthummelns västsida, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>404965</v>
+        <v>405040</v>
       </c>
       <c r="R12" t="n">
-        <v>7032021</v>
+        <v>7031813</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1845,12 +1848,13 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Grovvuxna skogsöar på skidbacke</t>
+          <t>Översilad, sluten grannaturskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1868,32 +1872,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128479457</v>
+        <v>128479804</v>
       </c>
       <c r="B13" t="n">
-        <v>88723</v>
+        <v>90264</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4405</v>
+        <v>245031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Borgsjömusseron</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Tricholoma borgsjoeënse</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>Jacobsson &amp; Muskos</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1906,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>405040</v>
+        <v>404933</v>
       </c>
       <c r="R13" t="n">
-        <v>7031813</v>
+        <v>7031810</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1974,48 +1978,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128479804</v>
+        <v>128478995</v>
       </c>
       <c r="B14" t="n">
-        <v>90237</v>
+        <v>79116</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>245031</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Borgsjömusseron</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tricholoma borgsjoeënse</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Jacobsson &amp; Muskos</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Totthummelns västsida, Jmt</t>
+          <t>Tottbacken, Tottbacken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>404933</v>
+        <v>404965</v>
       </c>
       <c r="R14" t="n">
-        <v>7031810</v>
+        <v>7032021</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2056,13 +2057,12 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Översilad, sluten grannaturskog</t>
+          <t>Grovvuxna skogsöar på skidbacke</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 17107-2025 artfynd.xlsx
+++ b/artfynd/A 17107-2025 artfynd.xlsx
@@ -1141,7 +1141,7 @@
         <v>128479022</v>
       </c>
       <c r="B6" t="n">
-        <v>96050</v>
+        <v>96056</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>128479181</v>
       </c>
       <c r="B7" t="n">
-        <v>88894</v>
+        <v>88899</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>128479163</v>
       </c>
       <c r="B8" t="n">
-        <v>92191</v>
+        <v>92196</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>128479322</v>
       </c>
       <c r="B9" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>128478996</v>
       </c>
       <c r="B10" t="n">
-        <v>92429</v>
+        <v>92434</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>128479384</v>
       </c>
       <c r="B11" t="n">
-        <v>88894</v>
+        <v>88899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1766,48 +1766,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128479457</v>
+        <v>128478995</v>
       </c>
       <c r="B12" t="n">
-        <v>88750</v>
+        <v>79120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4405</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Totthummelns västsida, Jmt</t>
+          <t>Tottbacken, Tottbacken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>405040</v>
+        <v>404965</v>
       </c>
       <c r="R12" t="n">
-        <v>7031813</v>
+        <v>7032021</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1848,13 +1845,12 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Översilad, sluten grannaturskog</t>
+          <t>Grovvuxna skogsöar på skidbacke</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1872,32 +1868,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128479804</v>
+        <v>128479457</v>
       </c>
       <c r="B13" t="n">
-        <v>90264</v>
+        <v>88754</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>245031</v>
+        <v>4405</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Borgsjömusseron</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tricholoma borgsjoeënse</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Jacobsson &amp; Muskos</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1910,10 +1906,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>404933</v>
+        <v>405040</v>
       </c>
       <c r="R13" t="n">
-        <v>7031810</v>
+        <v>7031813</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1978,45 +1974,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128478995</v>
+        <v>128479804</v>
       </c>
       <c r="B14" t="n">
-        <v>79116</v>
+        <v>90269</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>245031</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Borgsjömusseron</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma borgsjoeënse</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Jacobsson &amp; Muskos</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tottbacken, Tottbacken, Jmt</t>
+          <t>Totthummelns västsida, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>404965</v>
+        <v>404933</v>
       </c>
       <c r="R14" t="n">
-        <v>7032021</v>
+        <v>7031810</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2057,12 +2056,13 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Grovvuxna skogsöar på skidbacke</t>
+          <t>Översilad, sluten grannaturskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 17107-2025 artfynd.xlsx
+++ b/artfynd/A 17107-2025 artfynd.xlsx
@@ -1141,7 +1141,7 @@
         <v>128479022</v>
       </c>
       <c r="B6" t="n">
-        <v>96056</v>
+        <v>96063</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>128479181</v>
       </c>
       <c r="B7" t="n">
-        <v>88899</v>
+        <v>88904</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>128479163</v>
       </c>
       <c r="B8" t="n">
-        <v>92196</v>
+        <v>92201</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>128479322</v>
       </c>
       <c r="B9" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>128478996</v>
       </c>
       <c r="B10" t="n">
-        <v>92434</v>
+        <v>92439</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>128479384</v>
       </c>
       <c r="B11" t="n">
-        <v>88899</v>
+        <v>88904</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1766,45 +1766,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128478995</v>
+        <v>128479804</v>
       </c>
       <c r="B12" t="n">
-        <v>79120</v>
+        <v>90274</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>245031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Borgsjömusseron</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma borgsjoeënse</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Jacobsson &amp; Muskos</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tottbacken, Tottbacken, Jmt</t>
+          <t>Totthummelns västsida, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>404965</v>
+        <v>404933</v>
       </c>
       <c r="R12" t="n">
-        <v>7032021</v>
+        <v>7031810</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1845,12 +1848,13 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Grovvuxna skogsöar på skidbacke</t>
+          <t>Översilad, sluten grannaturskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1868,48 +1872,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128479457</v>
+        <v>128478995</v>
       </c>
       <c r="B13" t="n">
-        <v>88754</v>
+        <v>79120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4405</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Totthummelns västsida, Jmt</t>
+          <t>Tottbacken, Tottbacken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>405040</v>
+        <v>404965</v>
       </c>
       <c r="R13" t="n">
-        <v>7031813</v>
+        <v>7032021</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1950,13 +1951,12 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Översilad, sluten grannaturskog</t>
+          <t>Grovvuxna skogsöar på skidbacke</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1974,32 +1974,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128479804</v>
+        <v>128479457</v>
       </c>
       <c r="B14" t="n">
-        <v>90269</v>
+        <v>88755</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>245031</v>
+        <v>4405</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Borgsjömusseron</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tricholoma borgsjoeënse</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Jacobsson &amp; Muskos</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2012,10 +2012,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>404933</v>
+        <v>405040</v>
       </c>
       <c r="R14" t="n">
-        <v>7031810</v>
+        <v>7031813</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 17107-2025 artfynd.xlsx
+++ b/artfynd/A 17107-2025 artfynd.xlsx
@@ -1766,48 +1766,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128479804</v>
+        <v>128478995</v>
       </c>
       <c r="B12" t="n">
-        <v>90274</v>
+        <v>79120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>245031</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Borgsjömusseron</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tricholoma borgsjoeënse</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Jacobsson &amp; Muskos</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Totthummelns västsida, Jmt</t>
+          <t>Tottbacken, Tottbacken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>404933</v>
+        <v>404965</v>
       </c>
       <c r="R12" t="n">
-        <v>7031810</v>
+        <v>7032021</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1848,13 +1845,12 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Översilad, sluten grannaturskog</t>
+          <t>Grovvuxna skogsöar på skidbacke</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1872,45 +1868,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128478995</v>
+        <v>128479457</v>
       </c>
       <c r="B13" t="n">
-        <v>79120</v>
+        <v>88755</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>4405</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tottbacken, Tottbacken, Jmt</t>
+          <t>Totthummelns västsida, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>404965</v>
+        <v>405040</v>
       </c>
       <c r="R13" t="n">
-        <v>7032021</v>
+        <v>7031813</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1951,12 +1950,13 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Grovvuxna skogsöar på skidbacke</t>
+          <t>Översilad, sluten grannaturskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1974,32 +1974,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128479457</v>
+        <v>128479804</v>
       </c>
       <c r="B14" t="n">
-        <v>88755</v>
+        <v>90274</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4405</v>
+        <v>245031</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Borgsjömusseron</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Tricholoma borgsjoeënse</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>Jacobsson &amp; Muskos</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2012,10 +2012,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>405040</v>
+        <v>404933</v>
       </c>
       <c r="R14" t="n">
-        <v>7031813</v>
+        <v>7031810</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 17107-2025 artfynd.xlsx
+++ b/artfynd/A 17107-2025 artfynd.xlsx
@@ -1766,45 +1766,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128478995</v>
+        <v>128479804</v>
       </c>
       <c r="B12" t="n">
-        <v>79120</v>
+        <v>90274</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>245031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Borgsjömusseron</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma borgsjoeënse</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Jacobsson &amp; Muskos</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tottbacken, Tottbacken, Jmt</t>
+          <t>Totthummelns västsida, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>404965</v>
+        <v>404933</v>
       </c>
       <c r="R12" t="n">
-        <v>7032021</v>
+        <v>7031810</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1845,12 +1848,13 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Grovvuxna skogsöar på skidbacke</t>
+          <t>Översilad, sluten grannaturskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1868,48 +1872,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128479457</v>
+        <v>128478995</v>
       </c>
       <c r="B13" t="n">
-        <v>88755</v>
+        <v>79120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4405</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Totthummelns västsida, Jmt</t>
+          <t>Tottbacken, Tottbacken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>405040</v>
+        <v>404965</v>
       </c>
       <c r="R13" t="n">
-        <v>7031813</v>
+        <v>7032021</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1950,13 +1951,12 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Översilad, sluten grannaturskog</t>
+          <t>Grovvuxna skogsöar på skidbacke</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1974,32 +1974,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128479804</v>
+        <v>128479457</v>
       </c>
       <c r="B14" t="n">
-        <v>90274</v>
+        <v>88755</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>245031</v>
+        <v>4405</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Borgsjömusseron</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tricholoma borgsjoeënse</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Jacobsson &amp; Muskos</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2012,10 +2012,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>404933</v>
+        <v>405040</v>
       </c>
       <c r="R14" t="n">
-        <v>7031810</v>
+        <v>7031813</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 17107-2025 artfynd.xlsx
+++ b/artfynd/A 17107-2025 artfynd.xlsx
@@ -1141,7 +1141,7 @@
         <v>128479022</v>
       </c>
       <c r="B6" t="n">
-        <v>96063</v>
+        <v>96067</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>128479181</v>
       </c>
       <c r="B7" t="n">
-        <v>88904</v>
+        <v>88908</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>128479163</v>
       </c>
       <c r="B8" t="n">
-        <v>92201</v>
+        <v>92205</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>128479322</v>
       </c>
       <c r="B9" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>128478996</v>
       </c>
       <c r="B10" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>128479384</v>
       </c>
       <c r="B11" t="n">
-        <v>88904</v>
+        <v>88908</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>128479804</v>
       </c>
       <c r="B12" t="n">
-        <v>90274</v>
+        <v>90278</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>128478995</v>
       </c>
       <c r="B13" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>128479457</v>
       </c>
       <c r="B14" t="n">
-        <v>88755</v>
+        <v>88759</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 17107-2025 artfynd.xlsx
+++ b/artfynd/A 17107-2025 artfynd.xlsx
@@ -1766,32 +1766,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128479804</v>
+        <v>128479457</v>
       </c>
       <c r="B12" t="n">
-        <v>90278</v>
+        <v>88759</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>245031</v>
+        <v>4405</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Borgsjömusseron</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tricholoma borgsjoeënse</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Jacobsson &amp; Muskos</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>404933</v>
+        <v>405040</v>
       </c>
       <c r="R12" t="n">
-        <v>7031810</v>
+        <v>7031813</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1974,32 +1974,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128479457</v>
+        <v>128479804</v>
       </c>
       <c r="B14" t="n">
-        <v>88759</v>
+        <v>90278</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4405</v>
+        <v>245031</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Borgsjömusseron</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Tricholoma borgsjoeënse</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>Jacobsson &amp; Muskos</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2012,10 +2012,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>405040</v>
+        <v>404933</v>
       </c>
       <c r="R14" t="n">
-        <v>7031813</v>
+        <v>7031810</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 17107-2025 artfynd.xlsx
+++ b/artfynd/A 17107-2025 artfynd.xlsx
@@ -1141,7 +1141,7 @@
         <v>128479022</v>
       </c>
       <c r="B6" t="n">
-        <v>96067</v>
+        <v>96074</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>128479181</v>
       </c>
       <c r="B7" t="n">
-        <v>88908</v>
+        <v>88913</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>128479163</v>
       </c>
       <c r="B8" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>128479322</v>
       </c>
       <c r="B9" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>128478996</v>
       </c>
       <c r="B10" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>128479384</v>
       </c>
       <c r="B11" t="n">
-        <v>88908</v>
+        <v>88913</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>128479457</v>
       </c>
       <c r="B12" t="n">
-        <v>88759</v>
+        <v>88764</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>128478995</v>
       </c>
       <c r="B13" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>128479804</v>
       </c>
       <c r="B14" t="n">
-        <v>90278</v>
+        <v>90283</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 17107-2025 artfynd.xlsx
+++ b/artfynd/A 17107-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>69857830</v>
+        <v>95760309</v>
       </c>
       <c r="B2" t="n">
-        <v>77507</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89098</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>230405</v>
+        <v>4388</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Mönjevaxing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Hygrocybe miniata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Åreskutan, Jmt</t>
+          <t>Solstigen, Totthummeln, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>405216.8688689309</v>
+        <v>404814</v>
       </c>
       <c r="R2" t="n">
-        <v>7032101.695344632</v>
+        <v>7031737</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -747,22 +751,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-03-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-03-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-24</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Vid stig i granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,70 +770,72 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Willman</t>
+          <t>Lennart Iselius</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Willman</t>
+          <t>Lennart Iselius</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94586480</v>
+        <v>80514142</v>
       </c>
       <c r="B3" t="n">
-        <v>96232</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219795</v>
+        <v>103031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Solstigen, Åre, Jmt</t>
+          <t>Nalles klipp, Åre, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>405032.7787896675</v>
+        <v>404890</v>
       </c>
       <c r="R3" t="n">
-        <v>7031783.431085361</v>
+        <v>7031745</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -861,22 +862,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-06-30</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-06-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,76 +882,63 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Daniel Ochterbeck</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Daniel Ochterbeck</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95760309</v>
+        <v>128479181</v>
       </c>
       <c r="B4" t="n">
-        <v>86150</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4388</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mönjevaxskivling</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hygrocybe miniata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Solstigen, Totthummeln, Jmt</t>
+          <t>Tottbacken, Tottbacken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>404813.1979107516</v>
+        <v>405203</v>
       </c>
       <c r="R4" t="n">
-        <v>7031737.493720198</v>
+        <v>7032031</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,27 +962,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-08-24</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-08-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Vid stig i granskog</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,25 +980,30 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Grovvuxna skogsöar på skidbacke</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lennart Iselius</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lennart Iselius</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125961766</v>
+        <v>128479384</v>
       </c>
       <c r="B5" t="n">
-        <v>91263</v>
+        <v>89292</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1043,21 +1011,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,17 +1034,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Totthummelns östsida , Totthummelns östsida , Jmt</t>
+          <t>Totthummelns västsida, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>404816</v>
+        <v>405132</v>
       </c>
       <c r="R5" t="n">
-        <v>7031799</v>
+        <v>7031872</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,12 +1068,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,7 +1088,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog i östsluttning</t>
+          <t>Översilad, sluten grannaturskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1141,7 +1109,7 @@
         <v>128479022</v>
       </c>
       <c r="B6" t="n">
-        <v>96077</v>
+        <v>96543</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,32 +1208,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128479181</v>
+        <v>128479163</v>
       </c>
       <c r="B7" t="n">
-        <v>88915</v>
+        <v>92632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>510</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1278,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>405203</v>
+        <v>405188</v>
       </c>
       <c r="R7" t="n">
-        <v>7032031</v>
+        <v>7032094</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1346,10 +1314,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128479163</v>
+        <v>128479457</v>
       </c>
       <c r="B8" t="n">
-        <v>92213</v>
+        <v>89143</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,21 +1325,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>4405</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1380,14 +1348,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tottbacken, Tottbacken, Jmt</t>
+          <t>Totthummelns västsida, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>405188</v>
+        <v>405040</v>
       </c>
       <c r="R8" t="n">
-        <v>7032094</v>
+        <v>7031813</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,7 +1402,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Grovvuxna skogsöar på skidbacke</t>
+          <t>Översilad, sluten grannaturskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1452,48 +1420,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128479322</v>
+        <v>128478996</v>
       </c>
       <c r="B9" t="n">
-        <v>91533</v>
+        <v>92869</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Totthummelns västsida, Jmt</t>
+          <t>Tottbacken, Tottbacken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>405142</v>
+        <v>404965</v>
       </c>
       <c r="R9" t="n">
-        <v>7031890</v>
+        <v>7032021</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,13 +1499,12 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Översilad, sluten grannaturskog</t>
+          <t>Grovvuxna skogsöar på skidbacke</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1558,32 +1522,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128478996</v>
+        <v>128478995</v>
       </c>
       <c r="B10" t="n">
-        <v>92451</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1660,51 +1624,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128479384</v>
+        <v>94586480</v>
       </c>
       <c r="B11" t="n">
-        <v>88915</v>
+        <v>99017</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>219795</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Totthummelns västsida, Jmt</t>
+          <t>Solstigen, Åre, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>405132</v>
+        <v>405033</v>
       </c>
       <c r="R11" t="n">
-        <v>7031872</v>
+        <v>7031783</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1728,12 +1691,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1742,75 +1705,68 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Översilad, sluten grannaturskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128479457</v>
+        <v>69857830</v>
       </c>
       <c r="B12" t="n">
-        <v>88766</v>
+        <v>79328</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4405</v>
+        <v>230405</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Totthummelns västsida, Jmt</t>
+          <t>Åreskutan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>405040</v>
+        <v>405217</v>
       </c>
       <c r="R12" t="n">
-        <v>7031813</v>
+        <v>7032102</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1834,12 +1790,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2018-03-09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2018-03-09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1848,69 +1804,66 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Översilad, sluten grannaturskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Willman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Willman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128478995</v>
+        <v>128479804</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>90668</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>245031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Borgsjömusseron</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma borgsjoeënse</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Jacobsson &amp; Muskos</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tottbacken, Tottbacken, Jmt</t>
+          <t>Totthummelns västsida, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>404965</v>
+        <v>404933</v>
       </c>
       <c r="R13" t="n">
-        <v>7032021</v>
+        <v>7031810</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1951,12 +1904,13 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Grovvuxna skogsöar på skidbacke</t>
+          <t>Översilad, sluten grannaturskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1971,112 +1925,6 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>128479804</v>
-      </c>
-      <c r="B14" t="n">
-        <v>90285</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>245031</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Borgsjömusseron</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Tricholoma borgsjoeënse</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Jacobsson &amp; Muskos</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Totthummelns västsida, Jmt</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>404933</v>
-      </c>
-      <c r="R14" t="n">
-        <v>7031810</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Översilad, sluten grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17107-2025 artfynd.xlsx
+++ b/artfynd/A 17107-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128479181</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128479384</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128479022</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128479163</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1206,6 +1231,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95760309</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1312,6 +1342,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128479457</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128478996</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1516,6 +1556,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128478995</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1621,6 +1666,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80514142</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1720,6 +1770,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94586480</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1819,6 +1874,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69857830</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1925,8 +1985,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128479804</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>